--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/magallanes.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M191"/>
+  <dimension ref="A1:M197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -961,7 +961,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1063,7 +1063,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3617-10-CM25</t>
+          <t>3617-9-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3160.71</v>
+        <v>5155.08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3617-9-CM25</t>
+          <t>3617-10-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>5155.08</v>
+        <v>3160.71</v>
       </c>
     </row>
     <row r="13">
@@ -1551,7 +1551,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3130-316-CM25</t>
+          <t>3130-315-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2190.2</v>
+        <v>2498.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3130-315-CM25</t>
+          <t>3130-316-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2498.9</v>
+        <v>2190.2</v>
       </c>
     </row>
     <row r="21">
@@ -1978,7 +1978,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1109692-69-CM25</t>
+          <t>1109692-68-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2374.32</v>
+        <v>2281.15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1109692-68-CM25</t>
+          <t>1109692-69-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2281.15</v>
+        <v>2374.32</v>
       </c>
     </row>
     <row r="28">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5638,7 +5638,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3268-924-CM25</t>
+          <t>3268-925-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>6416.98</v>
+        <v>4523.87</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3268-925-CM25</t>
+          <t>3268-924-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>4523.87</v>
+        <v>6416.98</v>
       </c>
     </row>
     <row r="88">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6126,7 +6126,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>697-26-CM26</t>
+          <t>1057402-652-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>60.605.000-3</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>INSTITUTO ANTARTICO CHILENO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>4462.22</v>
+        <v>803.04</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1057402-652-CM26</t>
+          <t>697-26-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>60.605.000-3</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>INSTITUTO ANTARTICO CHILENO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>803.04</v>
+        <v>4462.22</v>
       </c>
     </row>
     <row r="96">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6980,7 +6980,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3130-5368-CM26</t>
+          <t>1162-26-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7000,17 +7000,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2107.76</v>
+        <v>1313.16</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1162-26-CM26</t>
+          <t>3130-5368-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7061,17 +7061,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1313.16</v>
+        <v>2107.76</v>
       </c>
     </row>
     <row r="110">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7590,7 +7590,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3166-79-CM26</t>
+          <t>3166-78-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.209.441-6</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>34085.56</v>
+        <v>43993.12</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>3166-78-CM26</t>
+          <t>3166-79-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>GRUPO NUVIX SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>78.209.441-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>43993.12</v>
+        <v>34085.56</v>
       </c>
     </row>
     <row r="120">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7834,7 +7834,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1162-28-CM26</t>
+          <t>717503-100-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.265.990-2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Asociación Chilena de Municipalidades</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1514.33</v>
+        <v>1652.85</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>902977-4-CM26</t>
+          <t>3197-25-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7915,17 +7915,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>61.962.600-1</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.724.952-7</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2928.91</v>
+        <v>6169.78</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1162-32-CM26</t>
+          <t>902977-4-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1842.39</v>
+        <v>2928.91</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3197-25-CM26</t>
+          <t>1162-28-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8037,17 +8037,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.962.600-1</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE PUERTO WILLIAMS</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>76.724.952-7</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>6169.78</v>
+        <v>1514.33</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3866-23-CM26</t>
+          <t>1162-32-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>69.251.300-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>4636.55</v>
+        <v>1842.39</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1057402-2332-CM26</t>
+          <t>3866-23-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8159,17 +8159,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>69.251.300-2</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>11453.28</v>
+        <v>4636.55</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3166-88-CM26</t>
+          <t>1057402-2332-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.102.027-9</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>GRUPO NUVIX SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>78.209.441-6</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1721.69</v>
+        <v>11453.28</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>935-58-CM26</t>
+          <t>3166-88-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.102.027-9</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>78.209.441-6</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>6626.56</v>
+        <v>1721.69</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1540-580-CM26</t>
+          <t>935-58-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>808.73</v>
+        <v>6626.56</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>4305-39-CM26</t>
+          <t>1540-580-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.943.400-5</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3521.07</v>
+        <v>808.73</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4720-2-CM26</t>
+          <t>3268-96-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1176.36</v>
+        <v>2089.7</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3268-96-CM26</t>
+          <t>4305-39-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>61.943.400-5</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2089.7</v>
+        <v>3521.07</v>
       </c>
     </row>
     <row r="134">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9176,7 +9176,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3130-5672-CM26</t>
+          <t>3268-192-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2333.41</v>
+        <v>1925.7</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3268-191-CM26</t>
+          <t>3130-5672-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>6821.18</v>
+        <v>2333.41</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3268-192-CM26</t>
+          <t>3268-191-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1925.7</v>
+        <v>6821.18</v>
       </c>
     </row>
     <row r="147">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10152,7 +10152,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>855-64-CM26</t>
+          <t>855-66-SE26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10211,13 +10211,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>51911.62</v>
+        <v>3650.58</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>709129-15-CM26</t>
+          <t>855-65-SE26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Ministerio Publico</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10257,28 +10257,32 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>3225.68</v>
+        <v>583.11</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>855-65-SE26</t>
+          <t>709129-15-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10303,12 +10307,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10318,32 +10322,28 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>583.11</v>
+        <v>3225.68</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>855-66-SE26</t>
+          <t>855-64-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10402,7 +10402,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>3650.58</v>
+        <v>51911.62</v>
       </c>
     </row>
     <row r="164">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10591,7 +10591,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1609-152-CM26</t>
+          <t>3130-5962-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10646,13 +10646,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2138.84</v>
+        <v>5466.52</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>3130-5962-CM26</t>
+          <t>1609-152-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10692,12 +10692,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10707,7 +10707,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>5466.52</v>
+        <v>2138.84</v>
       </c>
     </row>
     <row r="169">
@@ -10957,7 +10957,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>5338-354-CM26</t>
+          <t>5338-355-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10997,12 +10997,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>86.527.400-9</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>9344.57</v>
+        <v>5572.48</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>5338-355-CM26</t>
+          <t>5338-354-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11058,12 +11058,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>5572.48</v>
+        <v>9344.57</v>
       </c>
     </row>
     <row r="175">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>CENTRAL ODONTOLOGICA MAGALLANES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11750,7 +11750,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1038-205-CM26</t>
+          <t>1038-206-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -11790,12 +11790,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Equilibrium SpA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -11805,13 +11805,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>875.42</v>
+        <v>2436.91</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1038-206-CM26</t>
+          <t>1038-205-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2436.91</v>
+        <v>875.42</v>
       </c>
     </row>
     <row r="188">
@@ -12111,6 +12111,372 @@
       </c>
       <c r="M191" s="2" t="n">
         <v>1019.72</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>3617-108-CM26</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="n">
+        <v>8297.940000000001</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>4890-151-CM26</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>61.972.500-k</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="n">
+        <v>779.01</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>4305-135-CM26</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>61.943.400-5</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>86.527.400-9</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="n">
+        <v>1851.74</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>3268-731-CM26</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>61.103.021-5</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="n">
+        <v>3446.6</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>1057402-10309-CM26</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="n">
+        <v>745.98</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>3130-6670-CM26</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>61.102.029-5</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="n">
+        <v>1551.51</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/magallanes.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M197"/>
+  <dimension ref="A1:M200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -745,7 +745,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +932,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1002,7 +1010,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>874750-41-CM25</t>
+          <t>3617-10-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1027,12 +1035,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,22 +1050,26 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>21305.51</v>
+        <v>3160.71</v>
       </c>
     </row>
     <row r="11">
@@ -1111,7 +1123,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1124,7 +1140,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3617-10-CM25</t>
+          <t>874750-41-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1149,12 +1165,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,28 +1180,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3160.71</v>
+        <v>21305.51</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>855-11-CM25</t>
+          <t>855-13-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1233,20 +1253,24 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>55294.3</v>
+        <v>4893.59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>855-13-CM25</t>
+          <t>855-11-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1294,14 +1318,18 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4893.59</v>
+        <v>55294.3</v>
       </c>
     </row>
     <row r="15">
@@ -1416,7 +1444,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1509,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1574,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1639,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1704,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1830,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1895,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2021,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2086,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2151,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2216,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2281,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2346,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2472,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2598,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2663,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2728,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2793,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2858,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2923,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2988,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3053,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3118,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3183,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3248,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3313,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3378,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3259,7 +3395,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1540-1368-CM25</t>
+          <t>1038-131-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3284,12 +3420,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,28 +3435,32 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>14441.73</v>
+        <v>2224.13</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1038-131-CM25</t>
+          <t>1540-1368-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3345,12 +3485,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,22 +3500,26 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2224.13</v>
+        <v>14441.73</v>
       </c>
     </row>
     <row r="49">
@@ -3429,7 +3573,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3638,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3703,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3768,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3833,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3898,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3963,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4028,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4093,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4158,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3991,7 +4175,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>855-225-CM25</t>
+          <t>1965-449-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4016,12 +4200,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,22 +4215,26 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3121.74</v>
+        <v>2152.44</v>
       </c>
     </row>
     <row r="60">
@@ -4100,7 +4288,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4113,7 +4305,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1965-449-CM25</t>
+          <t>855-225-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4138,12 +4330,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,22 +4345,26 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2152.44</v>
+        <v>3121.74</v>
       </c>
     </row>
     <row r="62">
@@ -4283,7 +4479,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4544,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4609,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4674,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4739,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4804,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4869,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4934,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4999,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5064,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5129,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5255,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5320,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5385,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5450,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5515,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5580,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5645,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5710,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5775,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5840,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5966,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6031,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6157,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6222,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6287,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6352,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6417,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6482,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6547,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6248,7 +6564,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2983-11-CM26</t>
+          <t>1057402-874-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6273,12 +6589,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6296,20 +6612,24 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3447.32</v>
+        <v>1122.98</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1057402-874-CM26</t>
+          <t>2983-11-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6334,12 +6654,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6357,14 +6677,18 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1122.98</v>
+        <v>3447.32</v>
       </c>
     </row>
     <row r="98">
@@ -6418,7 +6742,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6868,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6933,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6998,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7063,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7128,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7193,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7258,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7323,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7388,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7453,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7518,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7224,7 +7596,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1079445-24-CM26</t>
+          <t>4589-84-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7249,12 +7621,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7272,20 +7644,24 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3376.45</v>
+        <v>1829.61</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1162-22-CM26</t>
+          <t>3617-30-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7305,17 +7681,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7701,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>86.527.400-9</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7716,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2430.09</v>
+        <v>5128.09</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3617-29-CM26</t>
+          <t>1079445-24-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7371,12 +7747,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.505.628-8</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7394,20 +7770,24 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>3777.43</v>
+        <v>3376.45</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3617-30-CM26</t>
+          <t>1162-22-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7427,17 +7807,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7447,28 +7827,32 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>5128.09</v>
+        <v>2430.09</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>4589-84-CM26</t>
+          <t>3617-29-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7493,12 +7877,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7516,14 +7900,18 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1829.61</v>
+        <v>3777.43</v>
       </c>
     </row>
     <row r="117">
@@ -7577,7 +7965,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8030,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8095,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8160,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8225,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7834,7 +8242,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>717503-100-CM26</t>
+          <t>3197-25-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7854,17 +8262,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>69.265.990-2</t>
+          <t>61.962.600-1</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Asociación Chilena de Municipalidades</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7874,12 +8282,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.724.952-7</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,13 +8297,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1652.85</v>
+        <v>6169.78</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3197-25-CM26</t>
+          <t>1162-32-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7915,17 +8323,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.962.600-1</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7935,28 +8343,32 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>76.724.952-7</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>6169.78</v>
+        <v>1842.39</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>902977-4-CM26</t>
+          <t>717503-100-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7981,12 +8393,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>69.265.990-2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>Asociación Chilena de Municipalidades</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7996,22 +8408,26 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2928.91</v>
+        <v>1652.85</v>
       </c>
     </row>
     <row r="125">
@@ -8065,7 +8481,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8078,7 +8498,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1162-32-CM26</t>
+          <t>902977-4-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8103,12 +8523,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8118,22 +8538,26 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1842.39</v>
+        <v>2928.91</v>
       </c>
     </row>
     <row r="127">
@@ -8187,7 +8611,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8676,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8741,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8806,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8871,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8936,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9001,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9066,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8749,7 +9205,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3268-139-CM26</t>
+          <t>4305-52-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8774,12 +9230,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>61.943.400-5</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8797,20 +9253,24 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2080.69</v>
+        <v>1814.54</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>4305-52-CM26</t>
+          <t>3268-139-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8835,12 +9295,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.943.400-5</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8858,14 +9318,18 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1814.54</v>
+        <v>2080.69</v>
       </c>
     </row>
     <row r="139">
@@ -8919,7 +9383,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9448,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9513,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9578,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9643,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9176,7 +9660,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3268-192-CM26</t>
+          <t>3268-191-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9216,28 +9700,32 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1925.7</v>
+        <v>6821.18</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3130-5672-CM26</t>
+          <t>3268-192-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9262,12 +9750,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9277,12 +9765,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9292,13 +9780,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2333.41</v>
+        <v>1925.7</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3268-191-CM26</t>
+          <t>3130-5672-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9323,12 +9811,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9346,14 +9834,18 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>6821.18</v>
+        <v>2333.41</v>
       </c>
     </row>
     <row r="147">
@@ -9407,7 +9899,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10025,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10090,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10155,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10220,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10285,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10411,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10537,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10602,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10667,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10152,7 +10684,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>855-66-SE26</t>
+          <t>855-69-SE26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10172,7 +10704,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -10192,12 +10724,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>79.722.860-5</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -10211,13 +10743,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3650.58</v>
+        <v>757.01</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>855-65-SE26</t>
+          <t>855-68-SE26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10237,7 +10769,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -10257,12 +10789,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>79.722.860-5</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -10276,13 +10808,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>583.11</v>
+        <v>494.16</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>709129-15-CM26</t>
+          <t>855-66-SE26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10307,12 +10839,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10322,28 +10854,32 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>3225.68</v>
+        <v>3650.58</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>855-64-CM26</t>
+          <t>855-67-SE26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10363,7 +10899,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -10383,12 +10919,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>79.722.860-5</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -10402,13 +10938,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>51911.62</v>
+        <v>21853.53</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1038-100-CM26</t>
+          <t>709129-15-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10423,22 +10959,22 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10448,28 +10984,32 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Equilibrium SpA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1028.02</v>
+        <v>3225.68</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1237328-248-CM26</t>
+          <t>855-64-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10484,22 +11024,22 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10509,28 +11049,32 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>18152.54</v>
+        <v>51911.62</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1000813-202-CM26</t>
+          <t>855-65-SE26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10545,22 +11089,22 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.999.040-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10570,28 +11114,32 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>MARANGUNIC HERMANOS LIMITADA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>80.586.800-7</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>915.54</v>
+        <v>583.11</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3130-5962-CM26</t>
+          <t>1038-100-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10606,7 +11154,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10616,12 +11164,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10631,12 +11179,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10646,13 +11194,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>5466.52</v>
+        <v>1028.02</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1609-152-CM26</t>
+          <t>1237328-248-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10667,7 +11215,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10677,12 +11225,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10692,28 +11240,32 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr"/>
+          <t>78.209.499-8</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>2138.84</v>
+        <v>18152.54</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1057402-5875-CM26</t>
+          <t>1000813-202-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10723,12 +11275,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10738,12 +11290,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.999.040-4</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10753,12 +11305,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>MARANGUNIC HERMANOS LIMITADA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>80.586.800-7</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10768,13 +11320,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>795.35</v>
+        <v>915.54</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>697-167-CM26</t>
+          <t>3130-5962-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10784,12 +11336,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10799,12 +11351,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>60.605.000-3</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>INSTITUTO ANTARTICO CHILENO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10822,20 +11374,24 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>2453.85</v>
+        <v>5466.52</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1540-1454-CM26</t>
+          <t>1609-152-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10845,12 +11401,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10860,12 +11416,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10875,28 +11431,32 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1332.19</v>
+        <v>2138.84</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>5338-353-CM26</t>
+          <t>1057402-5875-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10911,7 +11471,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10921,12 +11481,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10936,28 +11496,32 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>9315.68</v>
+        <v>795.35</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>5338-355-CM26</t>
+          <t>697-167-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10972,7 +11536,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10982,12 +11546,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>60.605.000-3</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>INSTITUTO ANTARTICO CHILENO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -10997,28 +11561,32 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>5572.48</v>
+        <v>2453.85</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>5338-354-CM26</t>
+          <t>1540-1454-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11033,7 +11601,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -11043,12 +11611,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11066,20 +11634,24 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>9344.57</v>
+        <v>1332.19</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1208985-88-CM26</t>
+          <t>5338-353-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11089,12 +11661,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11104,12 +11676,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11119,12 +11691,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>77.338.250-6</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11134,13 +11706,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>2381.47</v>
+        <v>9315.68</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1208985-89-CM26</t>
+          <t>5338-355-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11150,12 +11722,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -11165,12 +11737,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11180,12 +11752,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>86.527.400-9</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -11195,13 +11767,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>2686.56</v>
+        <v>5572.48</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>3268-487-CM26</t>
+          <t>5338-354-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11211,27 +11783,27 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11249,20 +11821,24 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>4144.78</v>
+        <v>9344.57</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>3268-503-CM26</t>
+          <t>1208985-88-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11277,22 +11853,22 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11310,20 +11886,24 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>3451.26</v>
+        <v>2381.47</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>3263-35-CM26</t>
+          <t>1208985-89-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11338,22 +11918,22 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>70.788.300-6</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11371,20 +11951,24 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>1037.47</v>
+        <v>2686.56</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>3241-216-CM26</t>
+          <t>3268-487-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11399,7 +11983,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11409,12 +11993,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.102.028-7</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11432,20 +12016,24 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>3015.19</v>
+        <v>4144.78</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>3241-217-CM26</t>
+          <t>3268-503-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11460,22 +12048,22 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>61.102.028-7</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11485,28 +12073,32 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1362.44</v>
+        <v>3451.26</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2663-471-CM26</t>
+          <t>3263-35-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11516,12 +12108,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11531,12 +12123,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>70.788.300-6</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11546,28 +12138,32 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>2226.78</v>
+        <v>1037.47</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1057402-8367-CM26</t>
+          <t>3241-216-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11577,27 +12173,27 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.028-7</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11615,20 +12211,24 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2347.01</v>
+        <v>3015.19</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1540-1817-CM26</t>
+          <t>3241-217-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11638,12 +12238,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11653,12 +12253,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.102.028-7</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11668,12 +12268,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>86.527.400-9</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11683,13 +12283,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1281.94</v>
+        <v>1362.44</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>3268-533-CM26</t>
+          <t>2663-471-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11704,7 +12304,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11714,12 +12314,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11729,12 +12329,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>86.527.400-9</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -11744,13 +12344,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>2669.5</v>
+        <v>2226.78</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1038-206-CM26</t>
+          <t>1057402-8367-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11765,7 +12365,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11775,12 +12375,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11790,28 +12390,32 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>2436.91</v>
+        <v>2347.01</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1038-205-CM26</t>
+          <t>1540-1817-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11826,7 +12430,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11836,12 +12440,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11851,28 +12455,32 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Equilibrium SpA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>875.42</v>
+        <v>1281.94</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>3595-346-CM26</t>
+          <t>3268-533-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11887,22 +12495,22 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11912,28 +12520,32 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>962.74</v>
+        <v>2669.5</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>3130-6477-CM26</t>
+          <t>1038-206-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11948,7 +12560,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11958,12 +12570,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11973,28 +12585,32 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>8052.61</v>
+        <v>2436.91</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>707427-46-CM26</t>
+          <t>1038-205-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12009,22 +12625,22 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12034,12 +12650,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>ECOFFICE COMPUTACION LIMITADA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>76.293.503-1</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -12049,13 +12665,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>14497.46</v>
+        <v>875.42</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1057402-9202-CM26</t>
+          <t>3595-346-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12070,7 +12686,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -12080,12 +12696,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12103,20 +12719,24 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1019.72</v>
+        <v>962.74</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>3617-108-CM26</t>
+          <t>3130-6477-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12126,27 +12746,27 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12164,20 +12784,24 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>8297.940000000001</v>
+        <v>8052.61</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>4890-151-CM26</t>
+          <t>707427-46-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12187,12 +12811,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -12202,12 +12826,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.972.500-k</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12217,12 +12841,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>ECOFFICE COMPUTACION LIMITADA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>76.293.503-1</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12232,13 +12856,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>779.01</v>
+        <v>14497.46</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>4305-135-CM26</t>
+          <t>1057402-9202-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12248,27 +12872,27 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.943.400-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12278,28 +12902,32 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>1851.74</v>
+        <v>1019.72</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>3268-731-CM26</t>
+          <t>3617-108-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12314,7 +12942,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -12324,12 +12952,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12347,20 +12975,24 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>3446.6</v>
+        <v>8297.940000000001</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1057402-10309-CM26</t>
+          <t>4890-151-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12375,22 +13007,22 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.972.500-k</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12408,20 +13040,24 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>745.98</v>
+        <v>779.01</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>3130-6670-CM26</t>
+          <t>4305-135-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12436,7 +13072,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -12446,12 +13082,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.943.400-5</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12461,12 +13097,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>86.527.400-9</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -12476,6 +13112,201 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
+        <v>1851.74</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>3268-731-CM26</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>61.103.021-5</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="n">
+        <v>3446.6</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>1057402-10309-CM26</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="n">
+        <v>745.98</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>3130-6670-CM26</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>61.102.029-5</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="n">
         <v>1551.51</v>
       </c>
     </row>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/magallanes.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/magallanes.xlsx
@@ -9773,7 +9773,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/magallanes.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M200"/>
+  <dimension ref="A1:M210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7340,7 +7340,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1162-26-CM26</t>
+          <t>3130-5368-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7360,17 +7360,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7399,13 +7399,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1313.16</v>
+        <v>2107.76</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3130-5368-CM26</t>
+          <t>1162-26-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7425,17 +7425,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2107.76</v>
+        <v>1313.16</v>
       </c>
     </row>
     <row r="110">
@@ -7722,7 +7722,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1079445-24-CM26</t>
+          <t>3617-29-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7781,7 +7781,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>3376.45</v>
+        <v>3777.43</v>
       </c>
     </row>
     <row r="115">
@@ -7852,7 +7852,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3617-29-CM26</t>
+          <t>1079445-24-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.505.628-8</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3777.43</v>
+        <v>3376.45</v>
       </c>
     </row>
     <row r="117">
@@ -7982,7 +7982,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3166-78-CM26</t>
+          <t>3166-80-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8022,12 +8022,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>GRUPO NUVIX SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>78.209.441-6</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -8041,13 +8041,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>43993.12</v>
+        <v>11514.17</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>3166-79-CM26</t>
+          <t>3166-78-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8087,17 +8087,17 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.209.441-6</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8106,13 +8106,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>34085.56</v>
+        <v>43993.12</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3166-80-CM26</t>
+          <t>3166-79-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8152,17 +8152,17 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>11514.17</v>
+        <v>34085.56</v>
       </c>
     </row>
     <row r="121">
@@ -8242,7 +8242,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3197-25-CM26</t>
+          <t>717503-100-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8262,17 +8262,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.962.600-1</t>
+          <t>69.265.990-2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>Asociación Chilena de Municipalidades</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8282,28 +8282,32 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>76.724.952-7</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>6169.78</v>
+        <v>1652.85</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1162-32-CM26</t>
+          <t>3197-25-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8323,17 +8327,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.962.600-1</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8343,32 +8347,28 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.724.952-7</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>1842.39</v>
+        <v>6169.78</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>717503-100-CM26</t>
+          <t>1162-32-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>69.265.990-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Asociación Chilena de Municipalidades</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8408,17 +8408,17 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8427,13 +8427,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1652.85</v>
+        <v>1842.39</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1162-28-CM26</t>
+          <t>902977-4-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8473,17 +8473,17 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8492,13 +8492,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1514.33</v>
+        <v>2928.91</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>902977-4-CM26</t>
+          <t>1162-28-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8523,12 +8523,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8538,17 +8538,17 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8557,13 +8557,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2928.91</v>
+        <v>1514.33</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3866-23-CM26</t>
+          <t>3166-88-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8583,17 +8583,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>69.251.300-2</t>
+          <t>61.102.027-9</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>78.209.441-6</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>4636.55</v>
+        <v>1721.69</v>
       </c>
     </row>
     <row r="128">
@@ -8693,7 +8693,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3166-88-CM26</t>
+          <t>3866-23-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8713,17 +8713,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.102.027-9</t>
+          <t>69.251.300-2</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>GRUPO NUVIX SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>78.209.441-6</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -8752,7 +8752,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1721.69</v>
+        <v>4636.55</v>
       </c>
     </row>
     <row r="130">
@@ -9335,7 +9335,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1109692-69-CM26</t>
+          <t>2019-14-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>62.000.760-9</t>
+          <t>60.511.122-k</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1093.94</v>
+        <v>4204.1</v>
       </c>
     </row>
     <row r="140">
@@ -9465,7 +9465,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2019-14-CM26</t>
+          <t>1109692-69-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9490,12 +9490,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>60.511.122-k</t>
+          <t>62.000.760-9</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9524,7 +9524,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>4204.1</v>
+        <v>1093.94</v>
       </c>
     </row>
     <row r="142">
@@ -9660,7 +9660,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3268-191-CM26</t>
+          <t>3268-192-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9700,12 +9700,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>6821.18</v>
+        <v>1925.7</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3268-192-CM26</t>
+          <t>3268-191-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1925.7</v>
+        <v>6821.18</v>
       </c>
     </row>
     <row r="146">
@@ -10176,7 +10176,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>4052-54-CM26</t>
+          <t>5338-237-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10196,17 +10196,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>69.251.200-6</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10216,26 +10216,22 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.527.400-9</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>6073.47</v>
+        <v>1954.84</v>
       </c>
     </row>
     <row r="153">
@@ -10306,7 +10302,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5338-237-CM26</t>
+          <t>4052-54-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10326,17 +10322,17 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>69.251.200-6</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10346,22 +10342,26 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1954.84</v>
+        <v>6073.47</v>
       </c>
     </row>
     <row r="155">
@@ -10688,7 +10688,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>855-69-SE26</t>
+          <t>855-64-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -10728,12 +10728,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>WINKLER LIMITADA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>79.722.860-5</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -10747,13 +10747,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>757.01</v>
+        <v>51911.62</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>855-68-SE26</t>
+          <t>709129-15-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10773,17 +10773,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10793,17 +10793,17 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>WINKLER LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>79.722.860-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10812,7 +10812,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>494.16</v>
+        <v>3225.68</v>
       </c>
     </row>
     <row r="162">
@@ -10948,7 +10948,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>709129-15-CM26</t>
+          <t>855-68-SE26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10968,17 +10968,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10988,17 +10988,17 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>79.722.860-5</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -11007,13 +11007,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>3225.68</v>
+        <v>494.16</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>855-64-CM26</t>
+          <t>855-69-SE26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -11053,12 +11053,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>79.722.860-5</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -11072,7 +11072,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>51911.62</v>
+        <v>757.01</v>
       </c>
     </row>
     <row r="166">
@@ -12167,7 +12167,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3241-216-CM26</t>
+          <t>3241-217-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -12207,32 +12207,28 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.527.400-9</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>3015.19</v>
+        <v>1362.44</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>3241-217-CM26</t>
+          <t>3241-216-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12252,7 +12248,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -12272,22 +12268,26 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1362.44</v>
+        <v>3015.19</v>
       </c>
     </row>
     <row r="185">
@@ -12549,7 +12549,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1038-206-CM26</t>
+          <t>1038-205-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12589,32 +12589,28 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.475.342-9</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>2436.91</v>
+        <v>875.42</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1038-205-CM26</t>
+          <t>1038-206-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12654,22 +12650,26 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Equilibrium SpA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>875.42</v>
+        <v>2436.91</v>
       </c>
     </row>
     <row r="191">
@@ -12931,7 +12931,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>3617-108-CM26</t>
+          <t>3617-109-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12971,32 +12971,28 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.527.400-9</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>8297.940000000001</v>
+        <v>10707.02</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>4890-151-CM26</t>
+          <t>3617-108-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13011,22 +13007,22 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.972.500-k</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -13055,13 +13051,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>779.01</v>
+        <v>8297.940000000001</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>4305-135-CM26</t>
+          <t>4890-151-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13076,22 +13072,22 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.943.400-5</t>
+          <t>61.972.500-k</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13101,28 +13097,32 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1851.74</v>
+        <v>779.01</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>3268-731-CM26</t>
+          <t>4305-135-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13137,7 +13137,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -13147,12 +13147,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>61.943.400-5</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -13162,32 +13162,28 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.527.400-9</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>3446.6</v>
+        <v>1851.74</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1057402-10309-CM26</t>
+          <t>3268-731-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13202,22 +13198,22 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13246,72 +13242,718 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>745.98</v>
+        <v>3446.6</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
+          <t>1057402-10309-CM26</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="n">
+        <v>745.98</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
           <t>3130-6670-CM26</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
+      <c r="B201" t="inlineStr">
         <is>
           <t>2239-8-LR25</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
+      <c r="C201" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
+      <c r="D201" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>61.102.029-5</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="n">
+        <v>1551.51</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>1208985-115-CM26</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="n">
+        <v>1325.37</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>874750-349-CM26</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>61.102.029-5</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Magallanes</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>61.607.903-4</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>LOGISTRA SPA</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>78.209.481-5</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="n">
+        <v>736.54</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2354-363-CM26</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>69.250.200-0</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>77.338.250-6</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="n">
+        <v>1069.42</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>4305-164-CM26</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>61.943.400-5</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
         <is>
           <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
-      <c r="J200" t="inlineStr">
+      <c r="J205" t="inlineStr">
         <is>
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
+      <c r="K205" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M200" s="2" t="n">
-        <v>1551.51</v>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="n">
+        <v>759.01</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>1540-2283-CM26</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>61.607.904-2</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="n">
+        <v>1181.65</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>3617-128-CM26</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="n">
+        <v>1552.18</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2348-455-CM26</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>69.250.200-0</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="n">
+        <v>6165.46</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>1057402-11011-CM26</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="n">
+        <v>758.58</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>697-322-CM26</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>60.605.000-3</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>INSTITUTO ANTARTICO CHILENO</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="n">
+        <v>1396.79</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/magallanes.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/magallanes.xlsx
@@ -969,7 +969,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -10322,7 +10322,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -11098,7 +11098,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -12122,7 +12122,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/magallanes.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M210"/>
+  <dimension ref="A1:M212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7596,7 +7596,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>4589-84-CM26</t>
+          <t>3617-29-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7621,12 +7621,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7655,13 +7655,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1829.61</v>
+        <v>3777.43</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3617-30-CM26</t>
+          <t>1162-22-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7681,17 +7681,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7701,28 +7701,32 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>5128.09</v>
+        <v>2430.09</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3617-29-CM26</t>
+          <t>1079445-24-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7747,12 +7751,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.505.628-8</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7781,13 +7785,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>3777.43</v>
+        <v>3376.45</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1162-22-CM26</t>
+          <t>3617-30-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7807,17 +7811,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7827,32 +7831,28 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.527.400-9</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2430.09</v>
+        <v>5128.09</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1079445-24-CM26</t>
+          <t>4589-84-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3376.45</v>
+        <v>1829.61</v>
       </c>
     </row>
     <row r="117">
@@ -7982,7 +7982,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3166-80-CM26</t>
+          <t>3166-79-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8022,17 +8022,17 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>11514.17</v>
+        <v>34085.56</v>
       </c>
     </row>
     <row r="119">
@@ -8112,7 +8112,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3166-79-CM26</t>
+          <t>3166-80-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8152,17 +8152,17 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>34085.56</v>
+        <v>11514.17</v>
       </c>
     </row>
     <row r="121">
@@ -8242,7 +8242,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>717503-100-CM26</t>
+          <t>1162-28-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8267,12 +8267,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>69.265.990-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Asociación Chilena de Municipalidades</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8282,17 +8282,17 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8301,13 +8301,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1652.85</v>
+        <v>1514.33</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3197-25-CM26</t>
+          <t>1162-32-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8327,17 +8327,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.962.600-1</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8347,28 +8347,32 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>76.724.952-7</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>6169.78</v>
+        <v>1842.39</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1162-32-CM26</t>
+          <t>3197-25-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8388,17 +8392,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.962.600-1</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8408,32 +8412,28 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.724.952-7</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1842.39</v>
+        <v>6169.78</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>902977-4-CM26</t>
+          <t>717503-100-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>69.265.990-2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>Asociación Chilena de Municipalidades</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8473,17 +8473,17 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8492,13 +8492,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2928.91</v>
+        <v>1652.85</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1162-28-CM26</t>
+          <t>902977-4-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8523,12 +8523,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8538,17 +8538,17 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8557,13 +8557,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1514.33</v>
+        <v>2928.91</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3166-88-CM26</t>
+          <t>3866-23-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8583,17 +8583,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.102.027-9</t>
+          <t>69.251.300-2</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>GRUPO NUVIX SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>78.209.441-6</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1721.69</v>
+        <v>4636.55</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1057402-2332-CM26</t>
+          <t>3166-88-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.027-9</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>78.209.441-6</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8687,13 +8687,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>11453.28</v>
+        <v>1721.69</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3866-23-CM26</t>
+          <t>1057402-2332-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8713,17 +8713,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>69.251.300-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8752,7 +8752,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>4636.55</v>
+        <v>11453.28</v>
       </c>
     </row>
     <row r="130">
@@ -9400,7 +9400,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1109692-70-CM26</t>
+          <t>1109692-69-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9440,17 +9440,17 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9459,13 +9459,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>998.39</v>
+        <v>1093.94</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1109692-69-CM26</t>
+          <t>1109692-70-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9505,17 +9505,17 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -9524,7 +9524,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1093.94</v>
+        <v>998.39</v>
       </c>
     </row>
     <row r="142">
@@ -9660,7 +9660,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3268-192-CM26</t>
+          <t>3130-5672-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9700,12 +9700,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1925.7</v>
+        <v>2333.41</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3268-191-CM26</t>
+          <t>3268-192-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9784,13 +9784,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>6821.18</v>
+        <v>1925.7</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3130-5672-CM26</t>
+          <t>3268-191-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9849,7 +9849,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2333.41</v>
+        <v>6821.18</v>
       </c>
     </row>
     <row r="147">
@@ -10176,7 +10176,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5338-237-CM26</t>
+          <t>4052-54-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>69.251.200-6</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10216,28 +10216,32 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1954.84</v>
+        <v>6073.47</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1687-15-CM26</t>
+          <t>5338-237-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10262,12 +10266,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10277,32 +10281,28 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.527.400-9</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>794.9</v>
+        <v>1954.84</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>4052-54-CM26</t>
+          <t>1687-15-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>69.251.200-6</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10361,7 +10361,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>6073.47</v>
+        <v>794.9</v>
       </c>
     </row>
     <row r="155">
@@ -10688,7 +10688,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>855-64-CM26</t>
+          <t>709129-15-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10708,17 +10708,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10728,17 +10728,17 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10747,13 +10747,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>51911.62</v>
+        <v>3225.68</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>709129-15-CM26</t>
+          <t>855-65-SE26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10773,17 +10773,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10793,17 +10793,17 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10812,7 +10812,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>3225.68</v>
+        <v>583.11</v>
       </c>
     </row>
     <row r="162">
@@ -11078,7 +11078,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>855-65-SE26</t>
+          <t>855-64-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11137,13 +11137,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>583.11</v>
+        <v>51911.62</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1038-100-CM26</t>
+          <t>1237328-248-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11183,28 +11183,32 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Equilibrium SpA</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
+          <t>78.209.499-8</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1028.02</v>
+        <v>18152.54</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1237328-248-CM26</t>
+          <t>1038-100-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11229,12 +11233,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11244,26 +11248,22 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.475.342-9</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>18152.54</v>
+        <v>1028.02</v>
       </c>
     </row>
     <row r="169">
@@ -11330,7 +11330,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3130-5962-CM26</t>
+          <t>1609-152-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11355,12 +11355,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11370,17 +11370,17 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -11389,13 +11389,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>5466.52</v>
+        <v>2138.84</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1609-152-CM26</t>
+          <t>3130-5962-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11435,17 +11435,17 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -11454,7 +11454,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2138.84</v>
+        <v>5466.52</v>
       </c>
     </row>
     <row r="172">
@@ -13699,7 +13699,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>3617-128-CM26</t>
+          <t>697-322-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13724,12 +13724,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.605.000-3</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>INSTITUTO ANTARTICO CHILENO</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13758,13 +13758,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1552.18</v>
+        <v>1396.79</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2348-455-CM26</t>
+          <t>3617-128-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13789,12 +13789,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13804,17 +13804,17 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -13823,13 +13823,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>6165.46</v>
+        <v>1552.18</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1057402-11011-CM26</t>
+          <t>2348-455-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13854,12 +13854,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13869,17 +13869,17 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -13888,13 +13888,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>758.58</v>
+        <v>6165.46</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>697-322-CM26</t>
+          <t>1057402-11011-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13919,12 +13919,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>60.605.000-3</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>INSTITUTO ANTARTICO CHILENO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13953,7 +13953,133 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>1396.79</v>
+        <v>758.58</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>874750-383-CM26</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>61.607.903-4</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>86.527.400-9</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="n">
+        <v>2401.49</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>5338-594-CM26</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>71.133.700-8</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="n">
+        <v>3812.37</v>
       </c>
     </row>
   </sheetData>
